--- a/data/trans_orig/P35_2023-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P35_2023-Estudios-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si su médico u otra persona le ha aconsejado que realice algún tipo de ejercicio físico en 2023</t>
+          <t>Población según si su médico u otra persona le ha aconsejado que realice algún tipo de ejercicio físico en 2023 (tasa de respuesta: 99,92%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -730,12 +730,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>28822</t>
+          <t>28467</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>50623</t>
+          <t>49756</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -745,12 +745,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>5,6%</t>
+          <t>5,53%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>9,83%</t>
+          <t>9,66%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>44372</t>
+          <t>44472</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>65511</t>
+          <t>66426</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -780,12 +780,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>5,9%</t>
+          <t>5,91%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>8,71%</t>
+          <t>8,83%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>79389</t>
+          <t>78626</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>109858</t>
+          <t>108561</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>6,27%</t>
+          <t>6,2%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>8,67%</t>
+          <t>8,57%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>8740</t>
+          <t>8884</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>21845</t>
+          <t>22835</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,12 +858,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,73%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>4,24%</t>
+          <t>4,43%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>24644</t>
+          <t>24826</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>41024</t>
+          <t>41542</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>3,28%</t>
+          <t>3,3%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>5,45%</t>
+          <t>5,52%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>37120</t>
+          <t>36481</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>57449</t>
+          <t>56599</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>2,93%</t>
+          <t>2,88%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>4,53%</t>
+          <t>4,47%</t>
         </is>
       </c>
     </row>
@@ -956,12 +956,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>149087</t>
+          <t>148010</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>186307</t>
+          <t>184991</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -971,12 +971,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>28,95%</t>
+          <t>28,74%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>36,18%</t>
+          <t>35,92%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -991,12 +991,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>262850</t>
+          <t>262167</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>305254</t>
+          <t>302829</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1006,12 +1006,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>34,94%</t>
+          <t>34,85%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>40,58%</t>
+          <t>40,26%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1026,12 +1026,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>420582</t>
+          <t>422865</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>475725</t>
+          <t>478746</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1041,12 +1041,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>33,19%</t>
+          <t>33,37%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>37,54%</t>
+          <t>37,78%</t>
         </is>
       </c>
     </row>
@@ -1069,12 +1069,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>274682</t>
+          <t>275573</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>314379</t>
+          <t>315493</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1084,12 +1084,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>53,34%</t>
+          <t>53,52%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>61,05%</t>
+          <t>61,27%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1104,12 +1104,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>362262</t>
+          <t>362866</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>405706</t>
+          <t>403874</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1119,12 +1119,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>48,16%</t>
+          <t>48,24%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>53,93%</t>
+          <t>53,69%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1139,12 +1139,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>651468</t>
+          <t>650479</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>709387</t>
+          <t>708898</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1154,12 +1154,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>51,41%</t>
+          <t>51,33%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>55,98%</t>
+          <t>55,94%</t>
         </is>
       </c>
     </row>
@@ -1299,12 +1299,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>124834</t>
+          <t>131246</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>224528</t>
+          <t>225291</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1314,12 +1314,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>5,45%</t>
+          <t>5,73%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>9,8%</t>
+          <t>9,84%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1334,12 +1334,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>132608</t>
+          <t>135847</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>218286</t>
+          <t>216572</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1349,12 +1349,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>5,93%</t>
+          <t>6,08%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>9,76%</t>
+          <t>9,69%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1369,12 +1369,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>290877</t>
+          <t>287991</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>424357</t>
+          <t>423670</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1384,12 +1384,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>6,43%</t>
+          <t>6,36%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>9,38%</t>
+          <t>9,36%</t>
         </is>
       </c>
     </row>
@@ -1412,12 +1412,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>37910</t>
+          <t>38597</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>73887</t>
+          <t>75365</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1427,12 +1427,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,69%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,23%</t>
+          <t>3,29%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1447,12 +1447,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>42699</t>
+          <t>44335</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>78331</t>
+          <t>79046</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1462,12 +1462,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>1,98%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>3,54%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1482,12 +1482,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>92847</t>
+          <t>94052</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>145223</t>
+          <t>143347</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1497,12 +1497,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>2,08%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,21%</t>
+          <t>3,17%</t>
         </is>
       </c>
     </row>
@@ -1525,12 +1525,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>306594</t>
+          <t>281078</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>491062</t>
+          <t>485745</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1540,12 +1540,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>13,39%</t>
+          <t>12,27%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>21,44%</t>
+          <t>21,21%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1560,12 +1560,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>338873</t>
+          <t>338565</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>533790</t>
+          <t>531223</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1575,12 +1575,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>15,16%</t>
+          <t>15,14%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>23,87%</t>
+          <t>23,76%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1595,12 +1595,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>693316</t>
+          <t>715423</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>996118</t>
+          <t>990754</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1610,12 +1610,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>15,32%</t>
+          <t>15,81%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>22,01%</t>
+          <t>21,89%</t>
         </is>
       </c>
     </row>
@@ -1638,12 +1638,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1526410</t>
+          <t>1529059</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>1821631</t>
+          <t>1833097</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1653,12 +1653,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>66,65%</t>
+          <t>66,76%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>79,54%</t>
+          <t>80,04%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1673,12 +1673,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>1421226</t>
+          <t>1426661</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>1744868</t>
+          <t>1715881</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1688,12 +1688,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>63,56%</t>
+          <t>63,81%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>78,04%</t>
+          <t>76,74%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1708,12 +1708,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>2990785</t>
+          <t>2994285</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>3439389</t>
+          <t>3430548</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1723,12 +1723,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>66,08%</t>
+          <t>66,15%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>75,99%</t>
+          <t>75,79%</t>
         </is>
       </c>
     </row>
@@ -1868,12 +1868,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>17339</t>
+          <t>17322</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>38530</t>
+          <t>39284</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1888,7 +1888,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>5,96%</t>
+          <t>6,08%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1903,12 +1903,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>10253</t>
+          <t>10193</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>25187</t>
+          <t>24335</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1918,12 +1918,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>1,54%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>3,82%</t>
+          <t>3,69%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1938,12 +1938,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>32087</t>
+          <t>31993</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>57515</t>
+          <t>58853</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1953,12 +1953,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>2,46%</t>
+          <t>2,45%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>4,4%</t>
+          <t>4,5%</t>
         </is>
       </c>
     </row>
@@ -1981,12 +1981,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>6142</t>
+          <t>6457</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>21373</t>
+          <t>21459</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1996,12 +1996,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>3,31%</t>
+          <t>3,32%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2016,12 +2016,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>6749</t>
+          <t>6987</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>19581</t>
+          <t>19844</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2031,12 +2031,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>2,97%</t>
+          <t>3,01%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2051,12 +2051,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>15383</t>
+          <t>15211</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>35824</t>
+          <t>35566</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2066,12 +2066,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,16%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>2,72%</t>
         </is>
       </c>
     </row>
@@ -2094,12 +2094,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>145239</t>
+          <t>147242</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>191829</t>
+          <t>193705</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2109,12 +2109,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>22,46%</t>
+          <t>22,77%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>29,67%</t>
+          <t>29,96%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2129,12 +2129,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>136255</t>
+          <t>136935</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>174441</t>
+          <t>174209</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2144,12 +2144,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>20,64%</t>
+          <t>20,75%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>26,43%</t>
+          <t>26,4%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2164,12 +2164,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>293385</t>
+          <t>291645</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>351648</t>
+          <t>352622</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2179,12 +2179,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>22,45%</t>
+          <t>22,32%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>26,91%</t>
+          <t>26,99%</t>
         </is>
       </c>
     </row>
@@ -2207,12 +2207,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>415772</t>
+          <t>413316</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>464919</t>
+          <t>463399</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2222,12 +2222,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>64,3%</t>
+          <t>63,92%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>71,9%</t>
+          <t>71,66%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2242,12 +2242,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>456759</t>
+          <t>456454</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>497350</t>
+          <t>496042</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2257,12 +2257,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>69,21%</t>
+          <t>69,16%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>75,36%</t>
+          <t>75,16%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2277,12 +2277,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>886178</t>
+          <t>885624</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>949910</t>
+          <t>950090</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2292,12 +2292,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>67,82%</t>
+          <t>67,78%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>72,7%</t>
+          <t>72,71%</t>
         </is>
       </c>
     </row>
@@ -2437,12 +2437,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>196191</t>
+          <t>193949</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>292674</t>
+          <t>289283</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2452,12 +2452,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>5,68%</t>
+          <t>5,62%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>8,48%</t>
+          <t>8,38%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2472,12 +2472,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>204437</t>
+          <t>208366</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>287236</t>
+          <t>286288</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2487,12 +2487,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>5,6%</t>
+          <t>5,71%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>7,87%</t>
+          <t>7,85%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2507,12 +2507,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>430911</t>
+          <t>433290</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>557316</t>
+          <t>562250</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2522,12 +2522,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>6,07%</t>
+          <t>6,1%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>7,85%</t>
+          <t>7,92%</t>
         </is>
       </c>
     </row>
@@ -2550,12 +2550,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>63102</t>
+          <t>62580</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>105162</t>
+          <t>101958</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2565,12 +2565,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>1,81%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>3,05%</t>
+          <t>2,95%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2585,12 +2585,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>84079</t>
+          <t>84028</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>127264</t>
+          <t>125066</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2605,7 +2605,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>3,49%</t>
+          <t>3,43%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2620,12 +2620,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>157835</t>
+          <t>156438</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>217973</t>
+          <t>219542</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2635,12 +2635,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>3,07%</t>
+          <t>3,09%</t>
         </is>
       </c>
     </row>
@@ -2663,12 +2663,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>591179</t>
+          <t>576766</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>834239</t>
+          <t>831672</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2678,12 +2678,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>17,13%</t>
+          <t>16,71%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>24,17%</t>
+          <t>24,09%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2698,12 +2698,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>727903</t>
+          <t>749665</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>979623</t>
+          <t>984567</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2713,12 +2713,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>19,95%</t>
+          <t>20,55%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>26,85%</t>
+          <t>26,99%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>1448174</t>
+          <t>1403662</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>1797295</t>
+          <t>1775972</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2748,12 +2748,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>20,4%</t>
+          <t>19,77%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>25,31%</t>
+          <t>25,01%</t>
         </is>
       </c>
     </row>
@@ -2776,12 +2776,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>2251735</t>
+          <t>2264156</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>2582130</t>
+          <t>2644463</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2791,12 +2791,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>65,23%</t>
+          <t>65,59%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>74,8%</t>
+          <t>76,61%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2811,12 +2811,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>2282528</t>
+          <t>2283451</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>2639038</t>
+          <t>2621320</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>62,57%</t>
+          <t>62,59%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>72,34%</t>
+          <t>71,85%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2846,12 +2846,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>4566736</t>
+          <t>4592996</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>5064607</t>
+          <t>5114042</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>64,32%</t>
+          <t>64,69%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>71,33%</t>
+          <t>72,03%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P35_2023-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P35_2023-Estudios-trans_orig.xlsx
@@ -725,32 +725,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>37916</t>
+          <t>43134</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>28467</t>
+          <t>31064</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>49756</t>
+          <t>56829</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>7,36%</t>
+          <t>7,46%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>5,53%</t>
+          <t>5,37%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>9,66%</t>
+          <t>9,82%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -760,32 +760,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>54914</t>
+          <t>61575</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>44472</t>
+          <t>51053</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>66426</t>
+          <t>74701</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>7,3%</t>
+          <t>7,51%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>5,91%</t>
+          <t>6,22%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>8,83%</t>
+          <t>9,11%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>92831</t>
+          <t>104709</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>78626</t>
+          <t>88824</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>108561</t>
+          <t>121706</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>7,33%</t>
+          <t>7,49%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>6,2%</t>
+          <t>6,35%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>8,57%</t>
+          <t>8,7%</t>
         </is>
       </c>
     </row>
@@ -838,22 +838,22 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>14428</t>
+          <t>15902</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>8884</t>
+          <t>10002</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>22835</t>
+          <t>24266</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>2,75%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -863,7 +863,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>4,43%</t>
+          <t>4,19%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>31572</t>
+          <t>36066</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>24826</t>
+          <t>27883</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>41542</t>
+          <t>45590</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>4,4%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>3,4%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>5,52%</t>
+          <t>5,56%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>46001</t>
+          <t>51968</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>36481</t>
+          <t>41603</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>56599</t>
+          <t>64531</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>3,63%</t>
+          <t>3,72%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>2,88%</t>
+          <t>2,97%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>4,47%</t>
+          <t>4,61%</t>
         </is>
       </c>
     </row>
@@ -951,32 +951,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>166087</t>
+          <t>178818</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>148010</t>
+          <t>157963</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>184991</t>
+          <t>199338</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>32,25%</t>
+          <t>30,91%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>28,74%</t>
+          <t>27,3%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>35,92%</t>
+          <t>34,46%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>282002</t>
+          <t>301381</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>262167</t>
+          <t>280559</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>302829</t>
+          <t>323669</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>37,49%</t>
+          <t>36,74%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>34,85%</t>
+          <t>34,2%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>40,26%</t>
+          <t>39,46%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>448089</t>
+          <t>480199</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>422865</t>
+          <t>450397</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>478746</t>
+          <t>509195</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>35,36%</t>
+          <t>34,33%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>33,37%</t>
+          <t>32,2%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>37,78%</t>
+          <t>36,4%</t>
         </is>
       </c>
     </row>
@@ -1064,32 +1064,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>296506</t>
+          <t>340675</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>275573</t>
+          <t>317181</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>315493</t>
+          <t>364022</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>57,58%</t>
+          <t>58,89%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>53,52%</t>
+          <t>54,83%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>61,27%</t>
+          <t>62,92%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1099,32 +1099,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>383734</t>
+          <t>421272</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>362866</t>
+          <t>399069</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>403874</t>
+          <t>442843</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>51,01%</t>
+          <t>51,36%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>48,24%</t>
+          <t>48,65%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>53,69%</t>
+          <t>53,99%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1134,32 +1134,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>680240</t>
+          <t>761947</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>650479</t>
+          <t>731254</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>708898</t>
+          <t>795495</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>53,68%</t>
+          <t>54,47%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>51,33%</t>
+          <t>52,28%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>55,94%</t>
+          <t>56,87%</t>
         </is>
       </c>
     </row>
@@ -1177,17 +1177,17 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>514938</t>
+          <t>578529</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>514938</t>
+          <t>578529</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>514938</t>
+          <t>578529</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1212,17 +1212,17 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>752222</t>
+          <t>820293</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>752222</t>
+          <t>820293</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>752222</t>
+          <t>820293</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1247,17 +1247,17 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>1267160</t>
+          <t>1398823</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1267160</t>
+          <t>1398823</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1267160</t>
+          <t>1398823</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1294,32 +1294,32 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>185923</t>
+          <t>213093</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>131246</t>
+          <t>185061</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>225291</t>
+          <t>253343</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>8,12%</t>
+          <t>9,55%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>5,73%</t>
+          <t>8,3%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>9,84%</t>
+          <t>11,36%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1329,32 +1329,32 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>181747</t>
+          <t>215750</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>135847</t>
+          <t>189011</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>216572</t>
+          <t>247224</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>8,13%</t>
+          <t>9,94%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>6,08%</t>
+          <t>8,71%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>9,69%</t>
+          <t>11,4%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1364,32 +1364,32 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>367670</t>
+          <t>428843</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>287991</t>
+          <t>386540</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>423670</t>
+          <t>477789</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>8,12%</t>
+          <t>9,75%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>6,36%</t>
+          <t>8,78%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>9,36%</t>
+          <t>10,86%</t>
         </is>
       </c>
     </row>
@@ -1407,32 +1407,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>56275</t>
+          <t>67167</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>38597</t>
+          <t>51992</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>75365</t>
+          <t>84816</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>2,46%</t>
+          <t>3,01%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>2,33%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,29%</t>
+          <t>3,8%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1442,32 +1442,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>62143</t>
+          <t>70698</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>44335</t>
+          <t>56557</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>79046</t>
+          <t>87349</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>2,78%</t>
+          <t>3,26%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>2,61%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>3,54%</t>
+          <t>4,03%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1477,32 +1477,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>118418</t>
+          <t>137865</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>94052</t>
+          <t>114191</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>143347</t>
+          <t>159680</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>2,62%</t>
+          <t>3,13%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>2,6%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,17%</t>
+          <t>3,63%</t>
         </is>
       </c>
     </row>
@@ -1520,32 +1520,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>422924</t>
+          <t>462800</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>281078</t>
+          <t>426025</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>485745</t>
+          <t>505440</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>18,47%</t>
+          <t>20,75%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>12,27%</t>
+          <t>19,1%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>21,21%</t>
+          <t>22,66%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1555,32 +1555,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>466053</t>
+          <t>517660</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>338565</t>
+          <t>483564</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>531223</t>
+          <t>554467</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>20,84%</t>
+          <t>23,86%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>15,14%</t>
+          <t>22,29%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>23,76%</t>
+          <t>25,56%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1590,32 +1590,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>888977</t>
+          <t>980461</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>715423</t>
+          <t>928209</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>990754</t>
+          <t>1033073</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>19,64%</t>
+          <t>22,28%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>15,81%</t>
+          <t>21,1%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>21,89%</t>
+          <t>23,48%</t>
         </is>
       </c>
     </row>
@@ -1633,32 +1633,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>1625205</t>
+          <t>1487506</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1529059</t>
+          <t>1438040</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>1833097</t>
+          <t>1534083</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>70,96%</t>
+          <t>66,69%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>66,76%</t>
+          <t>64,47%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>80,04%</t>
+          <t>68,78%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1668,32 +1668,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>1525970</t>
+          <t>1365336</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>1426661</t>
+          <t>1323865</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>1715881</t>
+          <t>1409071</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>68,25%</t>
+          <t>62,93%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>63,81%</t>
+          <t>61,02%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>76,74%</t>
+          <t>64,95%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1703,32 +1703,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>3151175</t>
+          <t>2852843</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>2994285</t>
+          <t>2790815</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>3430548</t>
+          <t>2925043</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>69,62%</t>
+          <t>64,84%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>66,15%</t>
+          <t>63,43%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>75,79%</t>
+          <t>66,48%</t>
         </is>
       </c>
     </row>
@@ -1746,17 +1746,17 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>2290327</t>
+          <t>2230566</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2290327</t>
+          <t>2230566</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>2290327</t>
+          <t>2230566</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1781,17 +1781,17 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>2235914</t>
+          <t>2169444</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>2235914</t>
+          <t>2169444</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>2235914</t>
+          <t>2169444</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1816,17 +1816,17 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>4526241</t>
+          <t>4400011</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>4526241</t>
+          <t>4400011</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>4526241</t>
+          <t>4400011</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1863,32 +1863,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>26945</t>
+          <t>28934</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>17322</t>
+          <t>18797</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>39284</t>
+          <t>43753</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>4,17%</t>
+          <t>4,07%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>2,68%</t>
+          <t>2,64%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>6,08%</t>
+          <t>6,15%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1898,22 +1898,22 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>16141</t>
+          <t>17650</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>10193</t>
+          <t>11286</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>24335</t>
+          <t>26974</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
@@ -1923,7 +1923,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>3,69%</t>
+          <t>3,67%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1933,32 +1933,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>43086</t>
+          <t>46584</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>31993</t>
+          <t>35283</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>58853</t>
+          <t>62669</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>3,22%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>2,44%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>4,5%</t>
+          <t>4,33%</t>
         </is>
       </c>
     </row>
@@ -1976,32 +1976,32 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>12265</t>
+          <t>15331</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>6457</t>
+          <t>7885</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>21459</t>
+          <t>24619</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>2,15%</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>1,11%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>3,32%</t>
+          <t>3,46%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2011,32 +2011,32 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>11596</t>
+          <t>13299</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>6987</t>
+          <t>7949</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>19844</t>
+          <t>25631</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>1,81%</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>3,01%</t>
+          <t>3,49%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2046,32 +2046,32 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>23861</t>
+          <t>28631</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>15211</t>
+          <t>18273</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>35566</t>
+          <t>41180</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>1,98%</t>
         </is>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,26%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>2,72%</t>
+          <t>2,85%</t>
         </is>
       </c>
     </row>
@@ -2089,32 +2089,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>167094</t>
+          <t>187430</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>147242</t>
+          <t>164491</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>193705</t>
+          <t>215222</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>25,84%</t>
+          <t>26,34%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>22,77%</t>
+          <t>23,12%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>29,96%</t>
+          <t>30,25%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2124,32 +2124,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>154350</t>
+          <t>175788</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>136935</t>
+          <t>155901</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>174209</t>
+          <t>196703</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>23,39%</t>
+          <t>23,94%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>20,75%</t>
+          <t>21,23%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>26,4%</t>
+          <t>26,78%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2159,32 +2159,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>321445</t>
+          <t>363218</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>291645</t>
+          <t>332278</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>352622</t>
+          <t>395385</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>24,6%</t>
+          <t>25,12%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>22,32%</t>
+          <t>22,98%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>26,99%</t>
+          <t>27,34%</t>
         </is>
       </c>
     </row>
@@ -2202,32 +2202,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>440319</t>
+          <t>479892</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>413316</t>
+          <t>452347</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>463399</t>
+          <t>504395</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>68,1%</t>
+          <t>67,44%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>63,92%</t>
+          <t>63,57%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>71,66%</t>
+          <t>70,88%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2237,32 +2237,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>477916</t>
+          <t>527655</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>456454</t>
+          <t>504526</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>496042</t>
+          <t>548817</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>72,41%</t>
+          <t>71,85%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>69,16%</t>
+          <t>68,7%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>75,16%</t>
+          <t>74,73%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2272,32 +2272,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>918235</t>
+          <t>1007547</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>885624</t>
+          <t>970219</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>950090</t>
+          <t>1038925</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>70,28%</t>
+          <t>69,68%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>67,78%</t>
+          <t>67,1%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>72,71%</t>
+          <t>71,85%</t>
         </is>
       </c>
     </row>
@@ -2315,17 +2315,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>646623</t>
+          <t>711587</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>646623</t>
+          <t>711587</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>646623</t>
+          <t>711587</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2350,17 +2350,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>660003</t>
+          <t>734393</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>660003</t>
+          <t>734393</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>660003</t>
+          <t>734393</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2385,17 +2385,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1306627</t>
+          <t>1445980</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1306627</t>
+          <t>1445980</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1306627</t>
+          <t>1445980</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2432,32 +2432,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>250784</t>
+          <t>285161</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>193949</t>
+          <t>254455</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>289283</t>
+          <t>323991</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>7,27%</t>
+          <t>8,1%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>5,62%</t>
+          <t>7,23%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>8,38%</t>
+          <t>9,2%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2467,32 +2467,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>252802</t>
+          <t>294975</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>208366</t>
+          <t>266607</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>286288</t>
+          <t>329775</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>6,93%</t>
+          <t>7,92%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>5,71%</t>
+          <t>7,16%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>7,85%</t>
+          <t>8,86%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2502,32 +2502,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>503586</t>
+          <t>580135</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>433290</t>
+          <t>535373</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>562250</t>
+          <t>632367</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>7,09%</t>
+          <t>8,01%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>6,1%</t>
+          <t>7,39%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>7,92%</t>
+          <t>8,73%</t>
         </is>
       </c>
     </row>
@@ -2545,32 +2545,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>82969</t>
+          <t>98401</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>62580</t>
+          <t>79902</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>101958</t>
+          <t>118655</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>2,79%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>2,27%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>2,95%</t>
+          <t>3,37%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2580,67 +2580,67 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>105312</t>
+          <t>120063</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>84028</t>
+          <t>102322</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>125066</t>
+          <t>139518</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>2,89%</t>
+          <t>3,22%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>2,75%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
+          <t>3,75%</t>
+        </is>
+      </c>
+      <c r="Q20" s="2" t="inlineStr">
+        <is>
+          <t>265</t>
+        </is>
+      </c>
+      <c r="R20" s="2" t="inlineStr">
+        <is>
+          <t>218463</t>
+        </is>
+      </c>
+      <c r="S20" s="2" t="inlineStr">
+        <is>
+          <t>192916</t>
+        </is>
+      </c>
+      <c r="T20" s="2" t="inlineStr">
+        <is>
+          <t>248387</t>
+        </is>
+      </c>
+      <c r="U20" s="2" t="inlineStr">
+        <is>
+          <t>3,02%</t>
+        </is>
+      </c>
+      <c r="V20" s="2" t="inlineStr">
+        <is>
+          <t>2,66%</t>
+        </is>
+      </c>
+      <c r="W20" s="2" t="inlineStr">
+        <is>
           <t>3,43%</t>
-        </is>
-      </c>
-      <c r="Q20" s="2" t="inlineStr">
-        <is>
-          <t>265</t>
-        </is>
-      </c>
-      <c r="R20" s="2" t="inlineStr">
-        <is>
-          <t>188281</t>
-        </is>
-      </c>
-      <c r="S20" s="2" t="inlineStr">
-        <is>
-          <t>156438</t>
-        </is>
-      </c>
-      <c r="T20" s="2" t="inlineStr">
-        <is>
-          <t>219542</t>
-        </is>
-      </c>
-      <c r="U20" s="2" t="inlineStr">
-        <is>
-          <t>2,65%</t>
-        </is>
-      </c>
-      <c r="V20" s="2" t="inlineStr">
-        <is>
-          <t>2,2%</t>
-        </is>
-      </c>
-      <c r="W20" s="2" t="inlineStr">
-        <is>
-          <t>3,09%</t>
         </is>
       </c>
     </row>
@@ -2658,32 +2658,32 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>756105</t>
+          <t>829048</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>576766</t>
+          <t>778126</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>831672</t>
+          <t>886173</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>21,9%</t>
+          <t>23,55%</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>16,71%</t>
+          <t>22,1%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>24,09%</t>
+          <t>25,17%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2693,32 +2693,32 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>902406</t>
+          <t>994830</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>749665</t>
+          <t>947819</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>984567</t>
+          <t>1039606</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>24,74%</t>
+          <t>26,71%</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>20,55%</t>
+          <t>25,45%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>26,99%</t>
+          <t>27,92%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2728,32 +2728,32 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>1658511</t>
+          <t>1823878</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>1403662</t>
+          <t>1760301</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>1775972</t>
+          <t>1897818</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>23,36%</t>
+          <t>25,17%</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>19,77%</t>
+          <t>24,3%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>25,01%</t>
+          <t>26,2%</t>
         </is>
       </c>
     </row>
@@ -2771,32 +2771,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>2362031</t>
+          <t>2308073</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>2264156</t>
+          <t>2243528</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>2644463</t>
+          <t>2369502</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>68,43%</t>
+          <t>65,56%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>65,59%</t>
+          <t>63,72%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>76,61%</t>
+          <t>67,3%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2806,32 +2806,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>2387620</t>
+          <t>2314263</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>2283451</t>
+          <t>2261621</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>2621320</t>
+          <t>2363564</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>65,45%</t>
+          <t>62,14%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>62,59%</t>
+          <t>60,73%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>71,85%</t>
+          <t>63,47%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2841,32 +2841,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>4749650</t>
+          <t>4622337</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>4592996</t>
+          <t>4545166</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>5114042</t>
+          <t>4700802</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>66,9%</t>
+          <t>63,8%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>64,69%</t>
+          <t>62,74%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>72,03%</t>
+          <t>64,89%</t>
         </is>
       </c>
     </row>
@@ -2884,17 +2884,17 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>3451889</t>
+          <t>3520683</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3451889</t>
+          <t>3520683</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3451889</t>
+          <t>3520683</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,17 +2919,17 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>3648139</t>
+          <t>3724130</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3648139</t>
+          <t>3724130</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3648139</t>
+          <t>3724130</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,17 +2954,17 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>7100028</t>
+          <t>7244813</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>7100028</t>
+          <t>7244813</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>7100028</t>
+          <t>7244813</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
